--- a/DÍA 4/Redondeo.xlsx
+++ b/DÍA 4/Redondeo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\DÍA 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC95229-D9E8-4D81-B057-3CDB317DD167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88A27E0-8BDB-4C2C-98A2-C3B747E7757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AB698C9C-3990-4F18-AD25-DD962E841999}"/>
   </bookViews>
@@ -1056,8 +1056,8 @@
         <v>11.5</v>
       </c>
       <c r="M7" s="34">
-        <f t="shared" ref="M7:M14" si="2">ROUNDDOWN(J7,2)</f>
-        <v>11.5</v>
+        <f>ROUNDDOWN(J7,0)</f>
+        <v>11</v>
       </c>
       <c r="N7" s="36">
         <f>ROUND(AVERAGE(C7:H7),2)</f>
@@ -1087,11 +1087,11 @@
         <v>56</v>
       </c>
       <c r="I8" s="20">
-        <f t="shared" ref="I8:I14" si="3">SUM(C8:H8)</f>
+        <f t="shared" ref="I8:I14" si="2">SUM(C8:H8)</f>
         <v>153</v>
       </c>
       <c r="J8" s="29">
-        <f t="shared" ref="J8:J14" si="4">AVERAGE(C8:H8)</f>
+        <f t="shared" ref="J8:J14" si="3">AVERAGE(C8:H8)</f>
         <v>25.5</v>
       </c>
       <c r="K8" s="34">
@@ -1103,8 +1103,8 @@
         <v>25.5</v>
       </c>
       <c r="M8" s="34">
-        <f t="shared" si="2"/>
-        <v>25.5</v>
+        <f t="shared" ref="M8:M14" si="4">ROUNDDOWN(J8,0)</f>
+        <v>25</v>
       </c>
       <c r="N8" s="36">
         <f t="shared" ref="N8:N14" si="5">ROUND(AVERAGE(C8:H8),2)</f>
@@ -1134,11 +1134,11 @@
         <v>6</v>
       </c>
       <c r="I9" s="20">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="J9" s="29">
         <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="J9" s="29">
-        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
       <c r="K9" s="34">
@@ -1150,8 +1150,8 @@
         <v>3.5</v>
       </c>
       <c r="M9" s="34">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="N9" s="36">
         <f t="shared" si="5"/>
@@ -1181,11 +1181,11 @@
         <v>9</v>
       </c>
       <c r="I10" s="20">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="J10" s="29">
         <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="J10" s="29">
-        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="K10" s="34">
@@ -1197,7 +1197,7 @@
         <v>8</v>
       </c>
       <c r="M10" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="N10" s="36">
@@ -1228,11 +1228,11 @@
         <v>4</v>
       </c>
       <c r="I11" s="20">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="J11" s="29">
         <f t="shared" si="3"/>
-        <v>123</v>
-      </c>
-      <c r="J11" s="29">
-        <f t="shared" si="4"/>
         <v>20.5</v>
       </c>
       <c r="K11" s="34">
@@ -1244,8 +1244,8 @@
         <v>20.5</v>
       </c>
       <c r="M11" s="34">
-        <f t="shared" si="2"/>
-        <v>20.5</v>
+        <f t="shared" si="4"/>
+        <v>20</v>
       </c>
       <c r="N11" s="36">
         <f t="shared" si="5"/>
@@ -1275,11 +1275,11 @@
         <v>12</v>
       </c>
       <c r="I12" s="20">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="J12" s="29">
         <f t="shared" si="3"/>
-        <v>103</v>
-      </c>
-      <c r="J12" s="29">
-        <f t="shared" si="4"/>
         <v>17.166666666666668</v>
       </c>
       <c r="K12" s="34">
@@ -1291,8 +1291,8 @@
         <v>17.170000000000002</v>
       </c>
       <c r="M12" s="34">
-        <f t="shared" si="2"/>
-        <v>17.16</v>
+        <f t="shared" si="4"/>
+        <v>17</v>
       </c>
       <c r="N12" s="36">
         <f t="shared" si="5"/>
@@ -1322,11 +1322,11 @@
         <v>67</v>
       </c>
       <c r="I13" s="20">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="J13" s="29">
         <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="J13" s="29">
-        <f t="shared" si="4"/>
         <v>17.5</v>
       </c>
       <c r="K13" s="34">
@@ -1338,8 +1338,8 @@
         <v>17.5</v>
       </c>
       <c r="M13" s="34">
-        <f t="shared" si="2"/>
-        <v>17.5</v>
+        <f t="shared" si="4"/>
+        <v>17</v>
       </c>
       <c r="N13" s="36">
         <f t="shared" si="5"/>
@@ -1369,11 +1369,11 @@
         <v>89</v>
       </c>
       <c r="I14" s="25">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J14" s="30">
         <f t="shared" si="3"/>
-        <v>154</v>
-      </c>
-      <c r="J14" s="30">
-        <f t="shared" si="4"/>
         <v>25.666666666666668</v>
       </c>
       <c r="K14" s="34">
@@ -1385,8 +1385,8 @@
         <v>25.67</v>
       </c>
       <c r="M14" s="34">
-        <f t="shared" si="2"/>
-        <v>25.66</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
       <c r="N14" s="36">
         <f t="shared" si="5"/>

--- a/DÍA 4/Redondeo.xlsx
+++ b/DÍA 4/Redondeo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\DÍA 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88A27E0-8BDB-4C2C-98A2-C3B747E7757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128AE152-0D78-4688-B706-5049805B0D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AB698C9C-3990-4F18-AD25-DD962E841999}"/>
   </bookViews>
@@ -163,9 +163,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -538,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -576,9 +573,6 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -591,9 +585,6 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -606,22 +597,7 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -629,11 +605,31 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1004,16 +1000,16 @@
       <c r="J6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="K6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="L6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="M6" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="N6" s="27" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1039,409 +1035,409 @@
       <c r="H7" s="14">
         <v>3</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="29">
         <f>SUM(C7:H7)</f>
         <v>69</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="30">
         <f>AVERAGE(C7:H7)</f>
         <v>11.5</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="28">
         <f t="shared" ref="K7:K14" si="0">ROUND(J7,2)</f>
         <v>11.5</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="28">
         <f t="shared" ref="L7:L14" si="1">ROUNDUP(J7,2)</f>
         <v>11.5</v>
       </c>
-      <c r="M7" s="34">
-        <f>ROUNDDOWN(J7,0)</f>
-        <v>11</v>
-      </c>
-      <c r="N7" s="36">
+      <c r="M7" s="28">
+        <f t="shared" ref="M7:M14" si="2">ROUNDDOWN(J7,2)</f>
+        <v>11.5</v>
+      </c>
+      <c r="N7" s="28">
         <f>ROUND(AVERAGE(C7:H7),2)</f>
         <v>11.5</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>26</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>24</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>19</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>11</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <v>17</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <v>56</v>
       </c>
-      <c r="I8" s="20">
-        <f t="shared" ref="I8:I14" si="2">SUM(C8:H8)</f>
+      <c r="I8" s="31">
+        <f t="shared" ref="I8:I14" si="3">SUM(C8:H8)</f>
         <v>153</v>
       </c>
-      <c r="J8" s="29">
-        <f t="shared" ref="J8:J14" si="3">AVERAGE(C8:H8)</f>
+      <c r="J8" s="32">
+        <f t="shared" ref="J8:J14" si="4">AVERAGE(C8:H8)</f>
         <v>25.5</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="28">
         <f t="shared" si="0"/>
         <v>25.5</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="28">
         <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="M8" s="34">
-        <f t="shared" ref="M8:M14" si="4">ROUNDDOWN(J8,0)</f>
-        <v>25</v>
-      </c>
-      <c r="N8" s="36">
+      <c r="M8" s="28">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="N8" s="28">
         <f t="shared" ref="N8:N14" si="5">ROUND(AVERAGE(C8:H8),2)</f>
         <v>25.5</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>1</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>2</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>3</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>4</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <v>5</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="18">
         <v>6</v>
       </c>
-      <c r="I9" s="20">
-        <f t="shared" si="2"/>
+      <c r="I9" s="31">
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="J9" s="29">
-        <f t="shared" si="3"/>
+      <c r="J9" s="32">
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="28">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="28">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="M9" s="34">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="N9" s="36">
+      <c r="M9" s="28">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="N9" s="28">
         <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>8</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>10</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>6</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>7</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <v>8</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <v>9</v>
       </c>
-      <c r="I10" s="20">
-        <f t="shared" si="2"/>
+      <c r="I10" s="31">
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="J10" s="29">
-        <f t="shared" si="3"/>
+      <c r="J10" s="32">
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="28">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="28">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="M10" s="34">
-        <f t="shared" si="4"/>
+      <c r="M10" s="28">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="28">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>25</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>31</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>22</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>20</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <v>21</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="18">
         <v>4</v>
       </c>
-      <c r="I11" s="20">
-        <f t="shared" si="2"/>
+      <c r="I11" s="31">
+        <f t="shared" si="3"/>
         <v>123</v>
       </c>
-      <c r="J11" s="29">
-        <f t="shared" si="3"/>
+      <c r="J11" s="32">
+        <f t="shared" si="4"/>
         <v>20.5</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="28">
         <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="28">
         <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
-      <c r="M11" s="34">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="N11" s="36">
+      <c r="M11" s="28">
+        <f t="shared" si="2"/>
+        <v>20.5</v>
+      </c>
+      <c r="N11" s="28">
         <f t="shared" si="5"/>
         <v>20.5</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>14</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>11</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>23</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>23</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <v>20</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <v>12</v>
       </c>
-      <c r="I12" s="20">
-        <f t="shared" si="2"/>
+      <c r="I12" s="31">
+        <f t="shared" si="3"/>
         <v>103</v>
       </c>
-      <c r="J12" s="29">
-        <f t="shared" si="3"/>
+      <c r="J12" s="32">
+        <f t="shared" si="4"/>
         <v>17.166666666666668</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="28">
         <f t="shared" si="0"/>
         <v>17.170000000000002</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="28">
         <f t="shared" si="1"/>
         <v>17.170000000000002</v>
       </c>
-      <c r="M12" s="34">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="N12" s="36">
+      <c r="M12" s="28">
+        <f t="shared" si="2"/>
+        <v>17.16</v>
+      </c>
+      <c r="N12" s="28">
         <f t="shared" si="5"/>
         <v>17.170000000000002</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="16">
         <v>7</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>8</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>11</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>7</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <v>5</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="18">
         <v>67</v>
       </c>
-      <c r="I13" s="20">
-        <f t="shared" si="2"/>
+      <c r="I13" s="31">
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="J13" s="29">
-        <f t="shared" si="3"/>
+      <c r="J13" s="32">
+        <f t="shared" si="4"/>
         <v>17.5</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="28">
         <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="28">
         <f t="shared" si="1"/>
         <v>17.5</v>
       </c>
-      <c r="M13" s="34">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="N13" s="36">
+      <c r="M13" s="28">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+      <c r="N13" s="28">
         <f t="shared" si="5"/>
         <v>17.5</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="20">
         <v>11</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="21">
         <v>18</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="21">
         <v>19</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="21">
         <v>10</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="21">
         <v>7</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="22">
         <v>89</v>
       </c>
-      <c r="I14" s="25">
-        <f t="shared" si="2"/>
+      <c r="I14" s="33">
+        <f t="shared" si="3"/>
         <v>154</v>
       </c>
-      <c r="J14" s="30">
-        <f t="shared" si="3"/>
+      <c r="J14" s="34">
+        <f t="shared" si="4"/>
         <v>25.666666666666668</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="28">
         <f t="shared" si="0"/>
         <v>25.67</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="28">
         <f t="shared" si="1"/>
         <v>25.67</v>
       </c>
-      <c r="M14" s="34">
-        <f t="shared" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="N14" s="36">
+      <c r="M14" s="28">
+        <f t="shared" si="2"/>
+        <v>25.66</v>
+      </c>
+      <c r="N14" s="28">
         <f t="shared" si="5"/>
         <v>25.67</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="26"/>
-      <c r="C15" s="27">
+      <c r="B15" s="23"/>
+      <c r="C15" s="35">
         <f>SUM(C7:C14)</f>
         <v>114</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="35">
         <f t="shared" ref="D15:G15" si="6">SUM(D7:D14)</f>
         <v>115</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="35">
         <f t="shared" si="6"/>
         <v>118</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="35">
         <f t="shared" si="6"/>
         <v>91</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="35">
         <f t="shared" si="6"/>
         <v>92</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="35">
         <f>SUM(H7:H14)</f>
         <v>246</v>
       </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="17" spans="7:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="7:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="7:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1454,7 +1450,7 @@
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="7:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I20" s="33"/>
+      <c r="I20" s="26"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:K14">
